--- a/output/pdf_financials_xlsx/ONAU.xlsx
+++ b/output/pdf_financials_xlsx/ONAU.xlsx
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.084577</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.190694</v>
       </c>
     </row>
     <row r="93">
@@ -3548,7 +3548,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3880,7 +3884,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ONAU.xlsx
+++ b/output/pdf_financials_xlsx/ONAU.xlsx
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.264151</v>
+        <v>0.020707</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.940127</v>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.264151</v>
+        <v>-0.020707</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.940127</v>
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.095628</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.13498</v>
       </c>
     </row>
     <row r="13">
@@ -946,10 +946,10 @@
         <v>-0.590127</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.270635</v>
+        <v>-11.175007</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.646746</v>
+        <v>-7.511766</v>
       </c>
     </row>
     <row r="28">
@@ -984,10 +984,10 @@
         <v>-0.590127</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.270635</v>
+        <v>-11.175007</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.646746</v>
+        <v>-7.511766</v>
       </c>
     </row>
     <row r="30">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.038615</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003743</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>5.858256</v>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.038615</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003743</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>5.858256</v>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">

--- a/output/pdf_financials_xlsx/ONAU.xlsx
+++ b/output/pdf_financials_xlsx/ONAU.xlsx
@@ -5284,7 +5284,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -6514,7 +6518,11 @@
           <t>Private Placement</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>1e-06</v>
       </c>
